--- a/output/predictions_2026.xlsx
+++ b/output/predictions_2026.xlsx
@@ -749,7 +749,7 @@
         <v>185276829.8694343</v>
       </c>
       <c r="C3" s="6">
-        <v>623553080.8921326</v>
+        <v>623553080.8921325</v>
       </c>
       <c r="D3" s="6">
         <v>126038610</v>
@@ -795,7 +795,7 @@
         <v>191354420.5233864</v>
       </c>
       <c r="C5" s="6">
-        <v>593356855.0657954</v>
+        <v>593356855.0657955</v>
       </c>
       <c r="D5" s="6">
         <v>42004996</v>
@@ -838,7 +838,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="6">
-        <v>198592010.9299968</v>
+        <v>198592010.9299969</v>
       </c>
       <c r="C7" s="6">
         <v>595807228.4087459</v>
@@ -864,7 +864,7 @@
         <v>201950379.0522418</v>
       </c>
       <c r="C8" s="3">
-        <v>635727944.3552259</v>
+        <v>635727944.355226</v>
       </c>
       <c r="D8" s="3">
         <v>51324340</v>
@@ -887,7 +887,7 @@
         <v>203881927.8084632</v>
       </c>
       <c r="C9" s="6">
-        <v>614936723.3479046</v>
+        <v>614936723.3479044</v>
       </c>
       <c r="D9" s="6">
         <v>271446755</v>
@@ -907,10 +907,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="3">
-        <v>213738222.1960625</v>
+        <v>213738222.1960626</v>
       </c>
       <c r="C10" s="3">
-        <v>629765991.3898178</v>
+        <v>629765991.389818</v>
       </c>
       <c r="D10" s="3">
         <v>116429626</v>
@@ -933,7 +933,7 @@
         <v>220174987.2432342</v>
       </c>
       <c r="C11" s="6">
-        <v>620204708.7153965</v>
+        <v>620204708.7153964</v>
       </c>
       <c r="D11" s="6">
         <v>193586314</v>
@@ -956,7 +956,7 @@
         <v>241573210.0778116</v>
       </c>
       <c r="C12" s="3">
-        <v>592308158.0984476</v>
+        <v>592308158.0984477</v>
       </c>
       <c r="D12" s="3">
         <v>135212500</v>
@@ -976,7 +976,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>259941164.6040252</v>
+        <v>259941164.6040253</v>
       </c>
       <c r="C13" s="6">
         <v>608075627.3723929</v>
@@ -1002,7 +1002,7 @@
         <v>2475771754.766472</v>
       </c>
       <c r="C14" s="9">
-        <v>7303917893.15903</v>
+        <v>7303917893.159029</v>
       </c>
       <c r="D14" s="9">
         <v>1962149005</v>
@@ -1014,7 +1014,7 @@
         <v>0.2617654156017943</v>
       </c>
       <c r="G14" s="10">
-        <v>0.1192424021739156</v>
+        <v>0.1192424021739154</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions_2026.xlsx
+++ b/output/predictions_2026.xlsx
@@ -12,13 +12,14 @@
     <sheet name="Material Breakdown" sheetId="3" r:id="rId3"/>
     <sheet name="Customer Monthly Qty" sheetId="4" r:id="rId4"/>
     <sheet name="Customer Monthly Rev" sheetId="5" r:id="rId5"/>
+    <sheet name="Customer-Material Monthly" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="138">
   <si>
     <t>Month</t>
   </si>
@@ -186,6 +187,222 @@
   </si>
   <si>
     <t>Others</t>
+  </si>
+  <si>
+    <t>STW8A2PD-H0</t>
+  </si>
+  <si>
+    <t>STW8A12D-E1</t>
+  </si>
+  <si>
+    <t>SCG0104A/TG104</t>
+  </si>
+  <si>
+    <t>SAW9A62E-E2(H)</t>
+  </si>
+  <si>
+    <t>STW8A2PD-E1(H)(DISTY)</t>
+  </si>
+  <si>
+    <t>SCW0104L/WH104-NZ</t>
+  </si>
+  <si>
+    <t>STW8A2PD-S1(DISTY)</t>
+  </si>
+  <si>
+    <t>STW8A2SD</t>
+  </si>
+  <si>
+    <t>SSW0193AF</t>
+  </si>
+  <si>
+    <t>STW8A12D-H1</t>
+  </si>
+  <si>
+    <t>STW8C12C-E0(R9-)(DISTY)</t>
+  </si>
+  <si>
+    <t>STW8A12D-E2(Disty)</t>
+  </si>
+  <si>
+    <t>SCW0104A/TWH104-HS</t>
+  </si>
+  <si>
+    <t>STW9A12D</t>
+  </si>
+  <si>
+    <t>STW8C2SA-WHT80-3030-0.65T-2C-2P</t>
+  </si>
+  <si>
+    <t>STW8F12D</t>
+  </si>
+  <si>
+    <t>SCW0104Y</t>
+  </si>
+  <si>
+    <t>SZ5-M3-W0-00(M3IZ)</t>
+  </si>
+  <si>
+    <t>STW8A2PD-E2(DISTY)</t>
+  </si>
+  <si>
+    <t>STF0A36BE-SL</t>
+  </si>
+  <si>
+    <t>STW0L8PA(DISTY)</t>
+  </si>
+  <si>
+    <t>STW9A2PD-H3</t>
+  </si>
+  <si>
+    <t>STW9A2PD-E200C100P</t>
+  </si>
+  <si>
+    <t>STW8E12YE</t>
+  </si>
+  <si>
+    <t>SAW8C72A</t>
+  </si>
+  <si>
+    <t>STW9A12D(Disty)</t>
+  </si>
+  <si>
+    <t>STW8A32E-HA</t>
+  </si>
+  <si>
+    <t>SCW0104D/TWH104-HE</t>
+  </si>
+  <si>
+    <t>SCW0104X</t>
+  </si>
+  <si>
+    <t>SCR0104A/FR104-II1</t>
+  </si>
+  <si>
+    <t>STW0L8PA-G500C10N000</t>
+  </si>
+  <si>
+    <t>STW8C2PA/3030</t>
+  </si>
+  <si>
+    <t>SZ5-M3-WW-C8(M3IZ)</t>
+  </si>
+  <si>
+    <t>STF0A36AF/SFT825N-S</t>
+  </si>
+  <si>
+    <t>STW8T36BE/STW8T36B</t>
+  </si>
+  <si>
+    <t>SAW8L60A</t>
+  </si>
+  <si>
+    <t>STW9A12D-E2</t>
+  </si>
+  <si>
+    <t>STW7C2SB-NT</t>
+  </si>
+  <si>
+    <t>SZDR5A0D(00S10000)</t>
+  </si>
+  <si>
+    <t>조명 PKG 개발 SAMPLE</t>
+  </si>
+  <si>
+    <t>STW0L8PA-G900C10N000</t>
+  </si>
+  <si>
+    <t>SZ5-M4-WN-C8</t>
+  </si>
+  <si>
+    <t>SAW9A62E</t>
+  </si>
+  <si>
+    <t>STW8C12E-E00000IZR9</t>
+  </si>
+  <si>
+    <t>SAW8A62E-E2(H)</t>
+  </si>
+  <si>
+    <t>STW8A2PD-B1</t>
+  </si>
+  <si>
+    <t>STW9A12D-H0</t>
+  </si>
+  <si>
+    <t>STW8A12D-H0</t>
+  </si>
+  <si>
+    <t>STW9A12D-H1</t>
+  </si>
+  <si>
+    <t>STW8A12D-S1(IZ)</t>
+  </si>
+  <si>
+    <t>STW8A12D-H0G</t>
+  </si>
+  <si>
+    <t>조명 POWER 시작실 SAMPLE</t>
+  </si>
+  <si>
+    <t>STW8A32E-H1</t>
+  </si>
+  <si>
+    <t>STW8A2PD-E3H10000</t>
+  </si>
+  <si>
+    <t>조명 3528 개발 SAMPLE</t>
+  </si>
+  <si>
+    <t>STW8A2PD-H4</t>
+  </si>
+  <si>
+    <t>STW8A2PD-B3</t>
+  </si>
+  <si>
+    <t>STW8A2PD-B2</t>
+  </si>
+  <si>
+    <t>STW8Q14D</t>
+  </si>
+  <si>
+    <t>STW8A2PD-H5</t>
+  </si>
+  <si>
+    <t>STWSC12S-E1H10000</t>
+  </si>
+  <si>
+    <t>STW7C2SB-NT-E1H1C100(DISTY)</t>
+  </si>
+  <si>
+    <t>STW9A12D-E1</t>
+  </si>
+  <si>
+    <t>STW9C2SB-S(DISTY)</t>
+  </si>
+  <si>
+    <t>STW0LAPA-E2H1C100</t>
+  </si>
+  <si>
+    <t>STW8C12E-E200C0IZP</t>
+  </si>
+  <si>
+    <t>STW8A32E-H4</t>
+  </si>
+  <si>
+    <t>SAWS1564A(Disty)</t>
+  </si>
+  <si>
+    <t>SAWS1063A(Disty)</t>
+  </si>
+  <si>
+    <t>SAWS0661A(Disty)</t>
+  </si>
+  <si>
+    <t>SMJD-3622012F-A21500</t>
+  </si>
+  <si>
+    <t>SMJD-4829016F-A21500</t>
   </si>
   <si>
     <t>Predicted
@@ -220,6 +437,9 @@
   </si>
   <si>
     <t>TOTAL (Top 15)</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -700,22 +920,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -772,7 +992,7 @@
         <v>192256307.1297719</v>
       </c>
       <c r="C4" s="3">
-        <v>581527546.0632377</v>
+        <v>581527546.0632378</v>
       </c>
       <c r="D4" s="3">
         <v>309460920</v>
@@ -795,7 +1015,7 @@
         <v>191354420.5233864</v>
       </c>
       <c r="C5" s="6">
-        <v>593356855.0657955</v>
+        <v>593356855.0657954</v>
       </c>
       <c r="D5" s="6">
         <v>42004996</v>
@@ -838,10 +1058,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="6">
-        <v>198592010.9299969</v>
+        <v>198592010.9299968</v>
       </c>
       <c r="C7" s="6">
-        <v>595807228.4087459</v>
+        <v>595807228.4087458</v>
       </c>
       <c r="D7" s="6">
         <v>391828679</v>
@@ -861,10 +1081,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="3">
-        <v>201950379.0522418</v>
+        <v>201950379.0522417</v>
       </c>
       <c r="C8" s="3">
-        <v>635727944.355226</v>
+        <v>635727944.3552259</v>
       </c>
       <c r="D8" s="3">
         <v>51324340</v>
@@ -884,7 +1104,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="6">
-        <v>203881927.8084632</v>
+        <v>203881927.8084631</v>
       </c>
       <c r="C9" s="6">
         <v>614936723.3479044</v>
@@ -933,7 +1153,7 @@
         <v>220174987.2432342</v>
       </c>
       <c r="C11" s="6">
-        <v>620204708.7153964</v>
+        <v>620204708.7153965</v>
       </c>
       <c r="D11" s="6">
         <v>193586314</v>
@@ -956,7 +1176,7 @@
         <v>241573210.0778116</v>
       </c>
       <c r="C12" s="3">
-        <v>592308158.0984477</v>
+        <v>592308158.0984478</v>
       </c>
       <c r="D12" s="3">
         <v>135212500</v>
@@ -1002,7 +1222,7 @@
         <v>2475771754.766472</v>
       </c>
       <c r="C14" s="9">
-        <v>7303917893.159029</v>
+        <v>7303917893.15903</v>
       </c>
       <c r="D14" s="9">
         <v>1962149005</v>
@@ -1014,7 +1234,7 @@
         <v>0.2617654156017943</v>
       </c>
       <c r="G14" s="10">
-        <v>0.1192424021739154</v>
+        <v>0.1192424021739156</v>
       </c>
     </row>
   </sheetData>
@@ -1040,10 +1260,10 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1213,7 +1433,7 @@
     </row>
     <row r="17" spans="1:3" ht="24" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="B17" s="15">
         <v>100.01</v>
@@ -1245,10 +1465,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1418,7 +1638,7 @@
     </row>
     <row r="17" spans="1:3" ht="24" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="B17" s="15">
         <v>100</v>
@@ -2194,7 +2414,7 @@
     </row>
     <row r="18" spans="1:14" ht="24" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="B18" s="9">
         <v>170597145</v>
@@ -3003,7 +3223,7 @@
     </row>
     <row r="18" spans="1:14" ht="24" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="B18" s="9">
         <v>609694892</v>
@@ -3043,6 +3263,5709 @@
       </c>
       <c r="N18" s="9">
         <v>7303917892</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFF6B9D"/>
+  </sheetPr>
+  <dimension ref="A1:O121"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="3" max="15" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3">
+        <v>981262</v>
+      </c>
+      <c r="D2" s="3">
+        <v>107883517</v>
+      </c>
+      <c r="E2" s="3">
+        <v>93591063</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>28035590</v>
+      </c>
+      <c r="H2" s="3">
+        <v>129994183</v>
+      </c>
+      <c r="I2" s="3">
+        <v>79703580</v>
+      </c>
+      <c r="J2" s="3">
+        <v>106212529</v>
+      </c>
+      <c r="K2" s="3">
+        <v>144086728</v>
+      </c>
+      <c r="L2" s="3">
+        <v>73197994</v>
+      </c>
+      <c r="M2" s="3">
+        <v>168830591</v>
+      </c>
+      <c r="N2" s="3">
+        <v>189613100</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1122130137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="6">
+        <v>62069275</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46631489</v>
+      </c>
+      <c r="E3" s="6">
+        <v>23736747</v>
+      </c>
+      <c r="F3" s="6">
+        <v>12482</v>
+      </c>
+      <c r="G3" s="6">
+        <v>51539193</v>
+      </c>
+      <c r="H3" s="6">
+        <v>24060122</v>
+      </c>
+      <c r="I3" s="6">
+        <v>48016913</v>
+      </c>
+      <c r="J3" s="6">
+        <v>32593014</v>
+      </c>
+      <c r="K3" s="6">
+        <v>37789433</v>
+      </c>
+      <c r="L3" s="6">
+        <v>40785827</v>
+      </c>
+      <c r="M3" s="6">
+        <v>9489486</v>
+      </c>
+      <c r="N3" s="6">
+        <v>41951395</v>
+      </c>
+      <c r="O3" s="6">
+        <v>418675379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3157879</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>29442929</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>33746544</v>
+      </c>
+      <c r="H4" s="3">
+        <v>23369956</v>
+      </c>
+      <c r="I4" s="3">
+        <v>17631795</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20760256</v>
+      </c>
+      <c r="K4" s="3">
+        <v>15551405</v>
+      </c>
+      <c r="L4" s="3">
+        <v>54932711</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>198593475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>62440388</v>
+      </c>
+      <c r="G5" s="6">
+        <v>19090593</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>6922046</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <v>16884016</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <v>105337042</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>19370348</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>12979440</v>
+      </c>
+      <c r="H6" s="3">
+        <v>5742004</v>
+      </c>
+      <c r="I6" s="3">
+        <v>11236407</v>
+      </c>
+      <c r="J6" s="3">
+        <v>14467487</v>
+      </c>
+      <c r="K6" s="3">
+        <v>481418</v>
+      </c>
+      <c r="L6" s="3">
+        <v>732</v>
+      </c>
+      <c r="M6" s="3">
+        <v>23532396</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>87810232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="6">
+        <v>20821643</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>19097592</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>23133779</v>
+      </c>
+      <c r="J7" s="6">
+        <v>3459466</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>66512480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7095521</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2953978</v>
+      </c>
+      <c r="F8" s="3">
+        <v>18355458</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6327477</v>
+      </c>
+      <c r="H8" s="3">
+        <v>947431</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2827829</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5869330</v>
+      </c>
+      <c r="K8" s="3">
+        <v>800793</v>
+      </c>
+      <c r="L8" s="3">
+        <v>2513343</v>
+      </c>
+      <c r="M8" s="3">
+        <v>306112</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2768732</v>
+      </c>
+      <c r="O8" s="3">
+        <v>50766004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="6">
+        <v>36734877</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>292454</v>
+      </c>
+      <c r="F9" s="6">
+        <v>3819633</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1568349</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>846877</v>
+      </c>
+      <c r="K9" s="6">
+        <v>11776</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>43273967</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3">
+        <v>535234</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4721379</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>24986765</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2253737</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2060008</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5881</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3670476</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2085391</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>40318871</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="6">
+        <v>11015321</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1688587</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1701552</v>
+      </c>
+      <c r="F11" s="6">
+        <v>12582320</v>
+      </c>
+      <c r="G11" s="6">
+        <v>2280309</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1008791</v>
+      </c>
+      <c r="I11" s="6">
+        <v>1102</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>844130</v>
+      </c>
+      <c r="L11" s="6">
+        <v>3278909</v>
+      </c>
+      <c r="M11" s="6">
+        <v>2457903</v>
+      </c>
+      <c r="N11" s="6">
+        <v>2311928</v>
+      </c>
+      <c r="O11" s="6">
+        <v>39170854</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>31246719</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3660527</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2768</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>16834</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <v>34926848</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="6">
+        <v>9188180</v>
+      </c>
+      <c r="D13" s="6">
+        <v>13802165</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3809502</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1244101</v>
+      </c>
+      <c r="I13" s="6">
+        <v>1123641</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <v>29167588</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3159978</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1852</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2917421</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1535900</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>4157932</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1884</v>
+      </c>
+      <c r="L14" s="3">
+        <v>7356321</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2821974</v>
+      </c>
+      <c r="N14" s="3">
+        <v>636628</v>
+      </c>
+      <c r="O14" s="3">
+        <v>22589891</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>3129977</v>
+      </c>
+      <c r="G15" s="6">
+        <v>7635</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <v>3458082</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
+        <v>5634383</v>
+      </c>
+      <c r="N15" s="6">
+        <v>7074981</v>
+      </c>
+      <c r="O15" s="6">
+        <v>19305058</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1589983</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3201595</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1416361</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3314740</v>
+      </c>
+      <c r="J16" s="3">
+        <v>2081907</v>
+      </c>
+      <c r="K16" s="3">
+        <v>3299268</v>
+      </c>
+      <c r="L16" s="3">
+        <v>4392128</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
+        <v>19295982</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
+        <v>16112766</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
+        <v>16112766</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4842587</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6489720</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>3603556</v>
+      </c>
+      <c r="O18" s="3">
+        <v>14935863</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1210647</v>
+      </c>
+      <c r="F19" s="6">
+        <v>6366055</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1297944</v>
+      </c>
+      <c r="H19" s="6">
+        <v>861301</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <v>352866</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1921904</v>
+      </c>
+      <c r="L19" s="6">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
+        <v>2750714</v>
+      </c>
+      <c r="O19" s="6">
+        <v>14761430</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>111091</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1785110</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1647685</v>
+      </c>
+      <c r="G20" s="3">
+        <v>3891287</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1045945</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2740802</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>6752</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2129631</v>
+      </c>
+      <c r="O20" s="3">
+        <v>13358304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="6">
+        <v>859522</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2020473</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
+        <v>572622</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6">
+        <v>495724</v>
+      </c>
+      <c r="J21" s="6">
+        <v>208606</v>
+      </c>
+      <c r="K21" s="6">
+        <v>2119747</v>
+      </c>
+      <c r="L21" s="6">
+        <v>3237557</v>
+      </c>
+      <c r="M21" s="6">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
+        <v>1089016</v>
+      </c>
+      <c r="O21" s="6">
+        <v>10603267</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>344678</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3607431</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>784741</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>214487</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1930854</v>
+      </c>
+      <c r="L22" s="3">
+        <v>214447</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1125</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1057043</v>
+      </c>
+      <c r="O22" s="3">
+        <v>8154806</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <v>648972</v>
+      </c>
+      <c r="H23" s="6">
+        <v>143550</v>
+      </c>
+      <c r="I23" s="6">
+        <v>5505839</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6">
+        <v>0</v>
+      </c>
+      <c r="L23" s="6">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6">
+        <v>0</v>
+      </c>
+      <c r="O23" s="6">
+        <v>6298362</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="3">
+        <v>6297917</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>6297917</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>243554</v>
+      </c>
+      <c r="F25" s="6">
+        <v>4774541</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6">
+        <v>480476</v>
+      </c>
+      <c r="L25" s="6">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6">
+        <v>286980</v>
+      </c>
+      <c r="N25" s="6">
+        <v>180178</v>
+      </c>
+      <c r="O25" s="6">
+        <v>5965729</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3">
+        <v>167916</v>
+      </c>
+      <c r="D26" s="3">
+        <v>903542</v>
+      </c>
+      <c r="E26" s="3">
+        <v>622890</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2196913</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>99078</v>
+      </c>
+      <c r="I26" s="3">
+        <v>35251</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2768</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>11710</v>
+      </c>
+      <c r="M26" s="3">
+        <v>396146</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>4436214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6">
+        <v>471</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
+        <v>4228178</v>
+      </c>
+      <c r="N27" s="6">
+        <v>0</v>
+      </c>
+      <c r="O27" s="6">
+        <v>4228649</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4056800</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>4056800</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="6">
+        <v>524739</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1573793</v>
+      </c>
+      <c r="E29" s="6">
+        <v>286282</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>318124</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6">
+        <v>172973</v>
+      </c>
+      <c r="K29" s="6">
+        <v>235527</v>
+      </c>
+      <c r="L29" s="6">
+        <v>365950</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6">
+        <v>565264</v>
+      </c>
+      <c r="O29" s="6">
+        <v>4042652</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="3">
+        <v>587708</v>
+      </c>
+      <c r="D30" s="3">
+        <v>148122</v>
+      </c>
+      <c r="E30" s="3">
+        <v>113943</v>
+      </c>
+      <c r="F30" s="3">
+        <v>998597</v>
+      </c>
+      <c r="G30" s="3">
+        <v>305399</v>
+      </c>
+      <c r="H30" s="3">
+        <v>225177</v>
+      </c>
+      <c r="I30" s="3">
+        <v>242354</v>
+      </c>
+      <c r="J30" s="3">
+        <v>55351</v>
+      </c>
+      <c r="K30" s="3">
+        <v>275096</v>
+      </c>
+      <c r="L30" s="3">
+        <v>351312</v>
+      </c>
+      <c r="M30" s="3">
+        <v>225083</v>
+      </c>
+      <c r="N30" s="3">
+        <v>226105</v>
+      </c>
+      <c r="O30" s="3">
+        <v>3754246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1376915</v>
+      </c>
+      <c r="D31" s="6">
+        <v>281431</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>449369</v>
+      </c>
+      <c r="G31" s="6">
+        <v>274859</v>
+      </c>
+      <c r="H31" s="6">
+        <v>207162</v>
+      </c>
+      <c r="I31" s="6">
+        <v>660965</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0</v>
+      </c>
+      <c r="L31" s="6">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0</v>
+      </c>
+      <c r="N31" s="6">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6">
+        <v>3250701</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
+        <v>277728</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1560308</v>
+      </c>
+      <c r="G32" s="3">
+        <v>152699</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>612494</v>
+      </c>
+      <c r="J32" s="3">
+        <v>345947</v>
+      </c>
+      <c r="K32" s="3">
+        <v>94211</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>3043387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="6">
+        <v>201500</v>
+      </c>
+      <c r="D33" s="6">
+        <v>177746</v>
+      </c>
+      <c r="E33" s="6">
+        <v>265868</v>
+      </c>
+      <c r="F33" s="6">
+        <v>549228</v>
+      </c>
+      <c r="G33" s="6">
+        <v>234139</v>
+      </c>
+      <c r="H33" s="6">
+        <v>54042</v>
+      </c>
+      <c r="I33" s="6">
+        <v>193883</v>
+      </c>
+      <c r="J33" s="6">
+        <v>66422</v>
+      </c>
+      <c r="K33" s="6">
+        <v>429602</v>
+      </c>
+      <c r="L33" s="6">
+        <v>257629</v>
+      </c>
+      <c r="M33" s="6">
+        <v>315116</v>
+      </c>
+      <c r="N33" s="6">
+        <v>192190</v>
+      </c>
+      <c r="O33" s="6">
+        <v>2937364</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>2821974</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>2821974</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6">
+        <v>2785614</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
+        <v>0</v>
+      </c>
+      <c r="N35" s="6">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6">
+        <v>2785614</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="3">
+        <v>104948</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1098457</v>
+      </c>
+      <c r="G36" s="3">
+        <v>10</v>
+      </c>
+      <c r="H36" s="3">
+        <v>112588</v>
+      </c>
+      <c r="I36" s="3">
+        <v>359124</v>
+      </c>
+      <c r="J36" s="3">
+        <v>87179</v>
+      </c>
+      <c r="K36" s="3">
+        <v>118706</v>
+      </c>
+      <c r="L36" s="3">
+        <v>351312</v>
+      </c>
+      <c r="M36" s="3">
+        <v>168812</v>
+      </c>
+      <c r="N36" s="3">
+        <v>84790</v>
+      </c>
+      <c r="O36" s="3">
+        <v>2485924</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>475</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6">
+        <v>1126</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6">
+        <v>346</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0</v>
+      </c>
+      <c r="L37" s="6">
+        <v>2189843</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0</v>
+      </c>
+      <c r="N37" s="6">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6">
+        <v>2191790</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1797474</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3">
+        <v>1797474</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6">
+        <v>355492</v>
+      </c>
+      <c r="E39" s="6">
+        <v>91155</v>
+      </c>
+      <c r="F39" s="6">
+        <v>786395</v>
+      </c>
+      <c r="G39" s="6">
+        <v>122159</v>
+      </c>
+      <c r="H39" s="6">
+        <v>108085</v>
+      </c>
+      <c r="I39" s="6">
+        <v>0</v>
+      </c>
+      <c r="J39" s="6">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6">
+        <v>90443</v>
+      </c>
+      <c r="L39" s="6">
+        <v>0</v>
+      </c>
+      <c r="M39" s="6">
+        <v>216079</v>
+      </c>
+      <c r="N39" s="6">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1769808</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>952375</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>346984</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3">
+        <v>1299360</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="6">
+        <v>39670</v>
+      </c>
+      <c r="D41" s="6">
+        <v>156639</v>
+      </c>
+      <c r="E41" s="6">
+        <v>199116</v>
+      </c>
+      <c r="F41" s="6">
+        <v>853800</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="6">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6">
+        <v>0</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6">
+        <v>0</v>
+      </c>
+      <c r="N41" s="6">
+        <v>0</v>
+      </c>
+      <c r="O41" s="6">
+        <v>1249225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>2928</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>1237221</v>
+      </c>
+      <c r="O42" s="3">
+        <v>1240148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6">
+        <v>1104913</v>
+      </c>
+      <c r="J43" s="6">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6">
+        <v>0</v>
+      </c>
+      <c r="L43" s="6">
+        <v>0</v>
+      </c>
+      <c r="M43" s="6">
+        <v>0</v>
+      </c>
+      <c r="N43" s="6">
+        <v>0</v>
+      </c>
+      <c r="O43" s="6">
+        <v>1104913</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>20360</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <v>904425</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>924785</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="6">
+        <v>789207</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6">
+        <v>0</v>
+      </c>
+      <c r="J45" s="6">
+        <v>103784</v>
+      </c>
+      <c r="K45" s="6">
+        <v>0</v>
+      </c>
+      <c r="L45" s="6">
+        <v>0</v>
+      </c>
+      <c r="M45" s="6">
+        <v>0</v>
+      </c>
+      <c r="N45" s="6">
+        <v>0</v>
+      </c>
+      <c r="O45" s="6">
+        <v>892991</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
+        <v>266619</v>
+      </c>
+      <c r="E46" s="3">
+        <v>68366</v>
+      </c>
+      <c r="F46" s="3">
+        <v>224684</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>20266</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>24908</v>
+      </c>
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
+        <v>105394</v>
+      </c>
+      <c r="M46" s="3">
+        <v>40627</v>
+      </c>
+      <c r="N46" s="3">
+        <v>45221</v>
+      </c>
+      <c r="O46" s="3">
+        <v>796085</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <v>231685</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6">
+        <v>240151</v>
+      </c>
+      <c r="J47" s="6">
+        <v>283676</v>
+      </c>
+      <c r="K47" s="6">
+        <v>0</v>
+      </c>
+      <c r="L47" s="6">
+        <v>0</v>
+      </c>
+      <c r="M47" s="6">
+        <v>0</v>
+      </c>
+      <c r="N47" s="6">
+        <v>0</v>
+      </c>
+      <c r="O47" s="6">
+        <v>755511</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>318124</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
+        <v>365950</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>684073</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>197502</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6">
+        <v>218569</v>
+      </c>
+      <c r="L49" s="6">
+        <v>0</v>
+      </c>
+      <c r="M49" s="6">
+        <v>234086</v>
+      </c>
+      <c r="N49" s="6">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6">
+        <v>650157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="3">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <v>564630</v>
+      </c>
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>564630</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="6">
+        <v>99176</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6">
+        <v>89730</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <v>120254</v>
+      </c>
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6">
+        <v>32692</v>
+      </c>
+      <c r="K51" s="6">
+        <v>0</v>
+      </c>
+      <c r="L51" s="6">
+        <v>69164</v>
+      </c>
+      <c r="M51" s="6">
+        <v>53176</v>
+      </c>
+      <c r="N51" s="6">
+        <v>0</v>
+      </c>
+      <c r="O51" s="6">
+        <v>464192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
+        <v>462880</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>462880</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0</v>
+      </c>
+      <c r="D53" s="6">
+        <v>222183</v>
+      </c>
+      <c r="E53" s="6">
+        <v>39880</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6">
+        <v>139974</v>
+      </c>
+      <c r="H53" s="6">
+        <v>55168</v>
+      </c>
+      <c r="I53" s="6">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6">
+        <v>0</v>
+      </c>
+      <c r="K53" s="6">
+        <v>0</v>
+      </c>
+      <c r="L53" s="6">
+        <v>0</v>
+      </c>
+      <c r="M53" s="6">
+        <v>0</v>
+      </c>
+      <c r="N53" s="6">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6">
+        <v>457205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="3">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3">
+        <v>29161</v>
+      </c>
+      <c r="E54" s="3">
+        <v>97421</v>
+      </c>
+      <c r="F54" s="3">
+        <v>199407</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>496</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
+        <v>94541</v>
+      </c>
+      <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>247</v>
+      </c>
+      <c r="O54" s="3">
+        <v>421274</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="6">
+        <v>37781</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6">
+        <v>101800</v>
+      </c>
+      <c r="H55" s="6">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6">
+        <v>97979</v>
+      </c>
+      <c r="L55" s="6">
+        <v>152235</v>
+      </c>
+      <c r="M55" s="6">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6">
+        <v>389795</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="3">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3">
+        <v>220324</v>
+      </c>
+      <c r="M56" s="3">
+        <v>169375</v>
+      </c>
+      <c r="N56" s="3">
+        <v>0</v>
+      </c>
+      <c r="O56" s="3">
+        <v>389698</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6">
+        <v>299579</v>
+      </c>
+      <c r="G57" s="6">
+        <v>127</v>
+      </c>
+      <c r="H57" s="6">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6">
+        <v>52758</v>
+      </c>
+      <c r="L57" s="6">
+        <v>0</v>
+      </c>
+      <c r="M57" s="6">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6">
+        <v>352464</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="3">
+        <v>104948</v>
+      </c>
+      <c r="D58" s="3">
+        <v>227737</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>11776</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>344461</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6">
+        <v>254</v>
+      </c>
+      <c r="H59" s="6">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6">
+        <v>0</v>
+      </c>
+      <c r="J59" s="6">
+        <v>329341</v>
+      </c>
+      <c r="K59" s="6">
+        <v>0</v>
+      </c>
+      <c r="L59" s="6">
+        <v>0</v>
+      </c>
+      <c r="M59" s="6">
+        <v>0</v>
+      </c>
+      <c r="N59" s="6">
+        <v>0</v>
+      </c>
+      <c r="O59" s="6">
+        <v>329596</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="3">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3">
+        <v>318124</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
+        <v>318124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0</v>
+      </c>
+      <c r="F61" s="6">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6">
+        <v>305399</v>
+      </c>
+      <c r="H61" s="6">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6">
+        <v>0</v>
+      </c>
+      <c r="J61" s="6">
+        <v>0</v>
+      </c>
+      <c r="K61" s="6">
+        <v>0</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0</v>
+      </c>
+      <c r="M61" s="6">
+        <v>0</v>
+      </c>
+      <c r="N61" s="6">
+        <v>0</v>
+      </c>
+      <c r="O61" s="6">
+        <v>305399</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="3">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3">
+        <v>194410</v>
+      </c>
+      <c r="E62" s="3">
+        <v>99700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>294110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0</v>
+      </c>
+      <c r="D63" s="6">
+        <v>54157</v>
+      </c>
+      <c r="E63" s="6">
+        <v>49138</v>
+      </c>
+      <c r="F63" s="6">
+        <v>168513</v>
+      </c>
+      <c r="G63" s="6">
+        <v>5726</v>
+      </c>
+      <c r="H63" s="6">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6">
+        <v>0</v>
+      </c>
+      <c r="J63" s="6">
+        <v>0</v>
+      </c>
+      <c r="K63" s="6">
+        <v>0</v>
+      </c>
+      <c r="L63" s="6">
+        <v>0</v>
+      </c>
+      <c r="M63" s="6">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6">
+        <v>0</v>
+      </c>
+      <c r="O63" s="6">
+        <v>277534</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C64" s="3">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>235527</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>235527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6">
+        <v>0</v>
+      </c>
+      <c r="J65" s="6">
+        <v>0</v>
+      </c>
+      <c r="K65" s="6">
+        <v>0</v>
+      </c>
+      <c r="L65" s="6">
+        <v>732</v>
+      </c>
+      <c r="M65" s="6">
+        <v>0</v>
+      </c>
+      <c r="N65" s="6">
+        <v>222219</v>
+      </c>
+      <c r="O65" s="6">
+        <v>222951</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="3">
+        <v>117542</v>
+      </c>
+      <c r="D66" s="3">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3">
+        <v>81973</v>
+      </c>
+      <c r="M66" s="3">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
+        <v>199514</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="6">
+        <v>163719</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6">
+        <v>0</v>
+      </c>
+      <c r="K67" s="6">
+        <v>0</v>
+      </c>
+      <c r="L67" s="6">
+        <v>0</v>
+      </c>
+      <c r="M67" s="6">
+        <v>0</v>
+      </c>
+      <c r="N67" s="6">
+        <v>0</v>
+      </c>
+      <c r="O67" s="6">
+        <v>163719</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3">
+        <v>64568</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3">
+        <v>74909</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>139477</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0</v>
+      </c>
+      <c r="E69" s="6">
+        <v>8546</v>
+      </c>
+      <c r="F69" s="6">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
+        <v>28147</v>
+      </c>
+      <c r="I69" s="6">
+        <v>1102</v>
+      </c>
+      <c r="J69" s="6">
+        <v>0</v>
+      </c>
+      <c r="K69" s="6">
+        <v>47398</v>
+      </c>
+      <c r="L69" s="6">
+        <v>88</v>
+      </c>
+      <c r="M69" s="6">
+        <v>0</v>
+      </c>
+      <c r="N69" s="6">
+        <v>35329</v>
+      </c>
+      <c r="O69" s="6">
+        <v>120609</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" s="3">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>48673</v>
+      </c>
+      <c r="H70" s="3">
+        <v>12666</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>15568</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>25322</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>102228</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" s="6">
+        <v>45337</v>
+      </c>
+      <c r="D71" s="6">
+        <v>14997</v>
+      </c>
+      <c r="E71" s="6">
+        <v>2564</v>
+      </c>
+      <c r="F71" s="6">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6">
+        <v>0</v>
+      </c>
+      <c r="I71" s="6">
+        <v>0</v>
+      </c>
+      <c r="J71" s="6">
+        <v>12454</v>
+      </c>
+      <c r="K71" s="6">
+        <v>7631</v>
+      </c>
+      <c r="L71" s="6">
+        <v>3952</v>
+      </c>
+      <c r="M71" s="6">
+        <v>14180</v>
+      </c>
+      <c r="N71" s="6">
+        <v>0</v>
+      </c>
+      <c r="O71" s="6">
+        <v>101116</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="3">
+        <v>2099</v>
+      </c>
+      <c r="D72" s="3">
+        <v>18515</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <v>12725</v>
+      </c>
+      <c r="H72" s="3">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3">
+        <v>22611</v>
+      </c>
+      <c r="L72" s="3">
+        <v>23421</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3">
+        <v>14132</v>
+      </c>
+      <c r="O72" s="3">
+        <v>93502</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="6">
+        <v>0</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0</v>
+      </c>
+      <c r="E73" s="6">
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6">
+        <v>53445</v>
+      </c>
+      <c r="H73" s="6">
+        <v>11822</v>
+      </c>
+      <c r="I73" s="6">
+        <v>0</v>
+      </c>
+      <c r="J73" s="6">
+        <v>0</v>
+      </c>
+      <c r="K73" s="6">
+        <v>19784</v>
+      </c>
+      <c r="L73" s="6">
+        <v>0</v>
+      </c>
+      <c r="M73" s="6">
+        <v>0</v>
+      </c>
+      <c r="N73" s="6">
+        <v>0</v>
+      </c>
+      <c r="O73" s="6">
+        <v>85051</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C74" s="3">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>81030</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>81030</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C75" s="6">
+        <v>0</v>
+      </c>
+      <c r="D75" s="6">
+        <v>0</v>
+      </c>
+      <c r="E75" s="6">
+        <v>0</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6">
+        <v>0</v>
+      </c>
+      <c r="I75" s="6">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6">
+        <v>0</v>
+      </c>
+      <c r="K75" s="6">
+        <v>0</v>
+      </c>
+      <c r="L75" s="6">
+        <v>0</v>
+      </c>
+      <c r="M75" s="6">
+        <v>0</v>
+      </c>
+      <c r="N75" s="6">
+        <v>73484</v>
+      </c>
+      <c r="O75" s="6">
+        <v>73484</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="3">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3">
+        <v>58240</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>58240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C77" s="6">
+        <v>0</v>
+      </c>
+      <c r="D77" s="6">
+        <v>0</v>
+      </c>
+      <c r="E77" s="6">
+        <v>0</v>
+      </c>
+      <c r="F77" s="6">
+        <v>0</v>
+      </c>
+      <c r="G77" s="6">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
+        <v>0</v>
+      </c>
+      <c r="I77" s="6">
+        <v>0</v>
+      </c>
+      <c r="J77" s="6">
+        <v>18058</v>
+      </c>
+      <c r="K77" s="6">
+        <v>0</v>
+      </c>
+      <c r="L77" s="6">
+        <v>0</v>
+      </c>
+      <c r="M77" s="6">
+        <v>0</v>
+      </c>
+      <c r="N77" s="6">
+        <v>0</v>
+      </c>
+      <c r="O77" s="6">
+        <v>18058</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" s="3">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3">
+        <v>9364</v>
+      </c>
+      <c r="J78" s="3">
+        <v>1384</v>
+      </c>
+      <c r="K78" s="3">
+        <v>0</v>
+      </c>
+      <c r="L78" s="3">
+        <v>6587</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0</v>
+      </c>
+      <c r="N78" s="3">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3">
+        <v>17335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C79" s="6">
+        <v>0</v>
+      </c>
+      <c r="D79" s="6">
+        <v>0</v>
+      </c>
+      <c r="E79" s="6">
+        <v>0</v>
+      </c>
+      <c r="F79" s="6">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6">
+        <v>0</v>
+      </c>
+      <c r="I79" s="6">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6">
+        <v>0</v>
+      </c>
+      <c r="K79" s="6">
+        <v>0</v>
+      </c>
+      <c r="L79" s="6">
+        <v>2928</v>
+      </c>
+      <c r="M79" s="6">
+        <v>563</v>
+      </c>
+      <c r="N79" s="6">
+        <v>12718</v>
+      </c>
+      <c r="O79" s="6">
+        <v>16209</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="3">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3">
+        <v>12482</v>
+      </c>
+      <c r="G80" s="3">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>0</v>
+      </c>
+      <c r="K80" s="3">
+        <v>0</v>
+      </c>
+      <c r="L80" s="3">
+        <v>0</v>
+      </c>
+      <c r="M80" s="3">
+        <v>0</v>
+      </c>
+      <c r="N80" s="3">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3">
+        <v>12482</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" s="6">
+        <v>0</v>
+      </c>
+      <c r="D81" s="6">
+        <v>0</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0</v>
+      </c>
+      <c r="F81" s="6">
+        <v>0</v>
+      </c>
+      <c r="G81" s="6">
+        <v>0</v>
+      </c>
+      <c r="H81" s="6">
+        <v>0</v>
+      </c>
+      <c r="I81" s="6">
+        <v>0</v>
+      </c>
+      <c r="J81" s="6">
+        <v>0</v>
+      </c>
+      <c r="K81" s="6">
+        <v>158</v>
+      </c>
+      <c r="L81" s="6">
+        <v>11830</v>
+      </c>
+      <c r="M81" s="6">
+        <v>0</v>
+      </c>
+      <c r="N81" s="6">
+        <v>0</v>
+      </c>
+      <c r="O81" s="6">
+        <v>11989</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" s="3">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3">
+        <v>4273</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
+        <v>5726</v>
+      </c>
+      <c r="H82" s="3">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3">
+        <v>0</v>
+      </c>
+      <c r="L82" s="3">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3">
+        <v>0</v>
+      </c>
+      <c r="N82" s="3">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C83" s="6">
+        <v>0</v>
+      </c>
+      <c r="D83" s="6">
+        <v>0</v>
+      </c>
+      <c r="E83" s="6">
+        <v>9495</v>
+      </c>
+      <c r="F83" s="6">
+        <v>0</v>
+      </c>
+      <c r="G83" s="6">
+        <v>0</v>
+      </c>
+      <c r="H83" s="6">
+        <v>0</v>
+      </c>
+      <c r="I83" s="6">
+        <v>0</v>
+      </c>
+      <c r="J83" s="6">
+        <v>0</v>
+      </c>
+      <c r="K83" s="6">
+        <v>0</v>
+      </c>
+      <c r="L83" s="6">
+        <v>0</v>
+      </c>
+      <c r="M83" s="6">
+        <v>0</v>
+      </c>
+      <c r="N83" s="6">
+        <v>0</v>
+      </c>
+      <c r="O83" s="6">
+        <v>9495</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C84" s="3">
+        <v>3148</v>
+      </c>
+      <c r="D84" s="3">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3">
+        <v>6241</v>
+      </c>
+      <c r="G84" s="3">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3">
+        <v>0</v>
+      </c>
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>9390</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C85" s="6">
+        <v>0</v>
+      </c>
+      <c r="D85" s="6">
+        <v>0</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0</v>
+      </c>
+      <c r="F85" s="6">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6">
+        <v>0</v>
+      </c>
+      <c r="H85" s="6">
+        <v>0</v>
+      </c>
+      <c r="I85" s="6">
+        <v>5508</v>
+      </c>
+      <c r="J85" s="6">
+        <v>3459</v>
+      </c>
+      <c r="K85" s="6">
+        <v>0</v>
+      </c>
+      <c r="L85" s="6">
+        <v>0</v>
+      </c>
+      <c r="M85" s="6">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6">
+        <v>0</v>
+      </c>
+      <c r="O85" s="6">
+        <v>8968</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86" s="3">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3">
+        <v>8783</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>8783</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C87" s="6">
+        <v>0</v>
+      </c>
+      <c r="D87" s="6">
+        <v>0</v>
+      </c>
+      <c r="E87" s="6">
+        <v>0</v>
+      </c>
+      <c r="F87" s="6">
+        <v>6241</v>
+      </c>
+      <c r="G87" s="6">
+        <v>0</v>
+      </c>
+      <c r="H87" s="6">
+        <v>0</v>
+      </c>
+      <c r="I87" s="6">
+        <v>0</v>
+      </c>
+      <c r="J87" s="6">
+        <v>0</v>
+      </c>
+      <c r="K87" s="6">
+        <v>0</v>
+      </c>
+      <c r="L87" s="6">
+        <v>2196</v>
+      </c>
+      <c r="M87" s="6">
+        <v>0</v>
+      </c>
+      <c r="N87" s="6">
+        <v>0</v>
+      </c>
+      <c r="O87" s="6">
+        <v>8437</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C88" s="3">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3">
+        <v>0</v>
+      </c>
+      <c r="E88" s="3">
+        <v>5697</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>5697</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="6">
+        <v>5667</v>
+      </c>
+      <c r="D89" s="6">
+        <v>0</v>
+      </c>
+      <c r="E89" s="6">
+        <v>0</v>
+      </c>
+      <c r="F89" s="6">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6">
+        <v>0</v>
+      </c>
+      <c r="H89" s="6">
+        <v>0</v>
+      </c>
+      <c r="I89" s="6">
+        <v>0</v>
+      </c>
+      <c r="J89" s="6">
+        <v>0</v>
+      </c>
+      <c r="K89" s="6">
+        <v>0</v>
+      </c>
+      <c r="L89" s="6">
+        <v>0</v>
+      </c>
+      <c r="M89" s="6">
+        <v>0</v>
+      </c>
+      <c r="N89" s="6">
+        <v>0</v>
+      </c>
+      <c r="O89" s="6">
+        <v>5667</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3">
+        <v>0</v>
+      </c>
+      <c r="E90" s="3">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3">
+        <v>5627</v>
+      </c>
+      <c r="N90" s="3">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3">
+        <v>5627</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91" s="6">
+        <v>0</v>
+      </c>
+      <c r="D91" s="6">
+        <v>0</v>
+      </c>
+      <c r="E91" s="6">
+        <v>0</v>
+      </c>
+      <c r="F91" s="6">
+        <v>0</v>
+      </c>
+      <c r="G91" s="6">
+        <v>0</v>
+      </c>
+      <c r="H91" s="6">
+        <v>4504</v>
+      </c>
+      <c r="I91" s="6">
+        <v>0</v>
+      </c>
+      <c r="J91" s="6">
+        <v>0</v>
+      </c>
+      <c r="K91" s="6">
+        <v>0</v>
+      </c>
+      <c r="L91" s="6">
+        <v>0</v>
+      </c>
+      <c r="M91" s="6">
+        <v>0</v>
+      </c>
+      <c r="N91" s="6">
+        <v>0</v>
+      </c>
+      <c r="O91" s="6">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3">
+        <v>3659</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>3659</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="6">
+        <v>0</v>
+      </c>
+      <c r="D93" s="6">
+        <v>0</v>
+      </c>
+      <c r="E93" s="6">
+        <v>0</v>
+      </c>
+      <c r="F93" s="6">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6">
+        <v>0</v>
+      </c>
+      <c r="I93" s="6">
+        <v>0</v>
+      </c>
+      <c r="J93" s="6">
+        <v>0</v>
+      </c>
+      <c r="K93" s="6">
+        <v>0</v>
+      </c>
+      <c r="L93" s="6">
+        <v>2196</v>
+      </c>
+      <c r="M93" s="6">
+        <v>0</v>
+      </c>
+      <c r="N93" s="6">
+        <v>0</v>
+      </c>
+      <c r="O93" s="6">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C94" s="3">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>2196</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C95" s="6">
+        <v>0</v>
+      </c>
+      <c r="D95" s="6">
+        <v>0</v>
+      </c>
+      <c r="E95" s="6">
+        <v>1424</v>
+      </c>
+      <c r="F95" s="6">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6">
+        <v>0</v>
+      </c>
+      <c r="I95" s="6">
+        <v>0</v>
+      </c>
+      <c r="J95" s="6">
+        <v>0</v>
+      </c>
+      <c r="K95" s="6">
+        <v>0</v>
+      </c>
+      <c r="L95" s="6">
+        <v>0</v>
+      </c>
+      <c r="M95" s="6">
+        <v>0</v>
+      </c>
+      <c r="N95" s="6">
+        <v>0</v>
+      </c>
+      <c r="O95" s="6">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="3">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>844</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" s="6">
+        <v>0</v>
+      </c>
+      <c r="D97" s="6">
+        <v>833</v>
+      </c>
+      <c r="E97" s="6">
+        <v>0</v>
+      </c>
+      <c r="F97" s="6">
+        <v>0</v>
+      </c>
+      <c r="G97" s="6">
+        <v>0</v>
+      </c>
+      <c r="H97" s="6">
+        <v>0</v>
+      </c>
+      <c r="I97" s="6">
+        <v>0</v>
+      </c>
+      <c r="J97" s="6">
+        <v>0</v>
+      </c>
+      <c r="K97" s="6">
+        <v>0</v>
+      </c>
+      <c r="L97" s="6">
+        <v>0</v>
+      </c>
+      <c r="M97" s="6">
+        <v>0</v>
+      </c>
+      <c r="N97" s="6">
+        <v>0</v>
+      </c>
+      <c r="O97" s="6">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="3">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3">
+        <v>0</v>
+      </c>
+      <c r="E98" s="3">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3">
+        <v>0</v>
+      </c>
+      <c r="I98" s="3">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3">
+        <v>0</v>
+      </c>
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3">
+        <v>732</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C99" s="6">
+        <v>0</v>
+      </c>
+      <c r="D99" s="6">
+        <v>0</v>
+      </c>
+      <c r="E99" s="6">
+        <v>0</v>
+      </c>
+      <c r="F99" s="6">
+        <v>0</v>
+      </c>
+      <c r="G99" s="6">
+        <v>0</v>
+      </c>
+      <c r="H99" s="6">
+        <v>0</v>
+      </c>
+      <c r="I99" s="6">
+        <v>0</v>
+      </c>
+      <c r="J99" s="6">
+        <v>0</v>
+      </c>
+      <c r="K99" s="6">
+        <v>0</v>
+      </c>
+      <c r="L99" s="6">
+        <v>0</v>
+      </c>
+      <c r="M99" s="6">
+        <v>563</v>
+      </c>
+      <c r="N99" s="6">
+        <v>0</v>
+      </c>
+      <c r="O99" s="6">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" s="3">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>475</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C101" s="6">
+        <v>0</v>
+      </c>
+      <c r="D101" s="6">
+        <v>0</v>
+      </c>
+      <c r="E101" s="6">
+        <v>0</v>
+      </c>
+      <c r="F101" s="6">
+        <v>0</v>
+      </c>
+      <c r="G101" s="6">
+        <v>0</v>
+      </c>
+      <c r="H101" s="6">
+        <v>0</v>
+      </c>
+      <c r="I101" s="6">
+        <v>0</v>
+      </c>
+      <c r="J101" s="6">
+        <v>0</v>
+      </c>
+      <c r="K101" s="6">
+        <v>471</v>
+      </c>
+      <c r="L101" s="6">
+        <v>0</v>
+      </c>
+      <c r="M101" s="6">
+        <v>0</v>
+      </c>
+      <c r="N101" s="6">
+        <v>0</v>
+      </c>
+      <c r="O101" s="6">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="3">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>450</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="6">
+        <v>0</v>
+      </c>
+      <c r="D103" s="6">
+        <v>0</v>
+      </c>
+      <c r="E103" s="6">
+        <v>0</v>
+      </c>
+      <c r="F103" s="6">
+        <v>0</v>
+      </c>
+      <c r="G103" s="6">
+        <v>0</v>
+      </c>
+      <c r="H103" s="6">
+        <v>0</v>
+      </c>
+      <c r="I103" s="6">
+        <v>0</v>
+      </c>
+      <c r="J103" s="6">
+        <v>450</v>
+      </c>
+      <c r="K103" s="6">
+        <v>0</v>
+      </c>
+      <c r="L103" s="6">
+        <v>0</v>
+      </c>
+      <c r="M103" s="6">
+        <v>0</v>
+      </c>
+      <c r="N103" s="6">
+        <v>0</v>
+      </c>
+      <c r="O103" s="6">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C104" s="3">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3">
+        <v>0</v>
+      </c>
+      <c r="K104" s="3">
+        <v>0</v>
+      </c>
+      <c r="L104" s="3">
+        <v>366</v>
+      </c>
+      <c r="M104" s="3">
+        <v>0</v>
+      </c>
+      <c r="N104" s="3">
+        <v>0</v>
+      </c>
+      <c r="O104" s="3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="6">
+        <v>0</v>
+      </c>
+      <c r="D105" s="6">
+        <v>0</v>
+      </c>
+      <c r="E105" s="6">
+        <v>0</v>
+      </c>
+      <c r="F105" s="6">
+        <v>0</v>
+      </c>
+      <c r="G105" s="6">
+        <v>0</v>
+      </c>
+      <c r="H105" s="6">
+        <v>0</v>
+      </c>
+      <c r="I105" s="6">
+        <v>0</v>
+      </c>
+      <c r="J105" s="6">
+        <v>0</v>
+      </c>
+      <c r="K105" s="6">
+        <v>0</v>
+      </c>
+      <c r="L105" s="6">
+        <v>0</v>
+      </c>
+      <c r="M105" s="6">
+        <v>0</v>
+      </c>
+      <c r="N105" s="6">
+        <v>353</v>
+      </c>
+      <c r="O105" s="6">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="3">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3">
+        <v>0</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3">
+        <v>346</v>
+      </c>
+      <c r="K106" s="3">
+        <v>0</v>
+      </c>
+      <c r="L106" s="3">
+        <v>0</v>
+      </c>
+      <c r="M106" s="3">
+        <v>0</v>
+      </c>
+      <c r="N106" s="3">
+        <v>0</v>
+      </c>
+      <c r="O106" s="3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C107" s="6">
+        <v>0</v>
+      </c>
+      <c r="D107" s="6">
+        <v>0</v>
+      </c>
+      <c r="E107" s="6">
+        <v>0</v>
+      </c>
+      <c r="F107" s="6">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6">
+        <v>0</v>
+      </c>
+      <c r="H107" s="6">
+        <v>0</v>
+      </c>
+      <c r="I107" s="6">
+        <v>0</v>
+      </c>
+      <c r="J107" s="6">
+        <v>0</v>
+      </c>
+      <c r="K107" s="6">
+        <v>0</v>
+      </c>
+      <c r="L107" s="6">
+        <v>293</v>
+      </c>
+      <c r="M107" s="6">
+        <v>0</v>
+      </c>
+      <c r="N107" s="6">
+        <v>0</v>
+      </c>
+      <c r="O107" s="6">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C108" s="3">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3">
+        <v>0</v>
+      </c>
+      <c r="K108" s="3">
+        <v>188</v>
+      </c>
+      <c r="L108" s="3">
+        <v>0</v>
+      </c>
+      <c r="M108" s="3">
+        <v>0</v>
+      </c>
+      <c r="N108" s="3">
+        <v>0</v>
+      </c>
+      <c r="O108" s="3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C109" s="6">
+        <v>0</v>
+      </c>
+      <c r="D109" s="6">
+        <v>0</v>
+      </c>
+      <c r="E109" s="6">
+        <v>0</v>
+      </c>
+      <c r="F109" s="6">
+        <v>0</v>
+      </c>
+      <c r="G109" s="6">
+        <v>0</v>
+      </c>
+      <c r="H109" s="6">
+        <v>0</v>
+      </c>
+      <c r="I109" s="6">
+        <v>0</v>
+      </c>
+      <c r="J109" s="6">
+        <v>0</v>
+      </c>
+      <c r="K109" s="6">
+        <v>0</v>
+      </c>
+      <c r="L109" s="6">
+        <v>0</v>
+      </c>
+      <c r="M109" s="6">
+        <v>0</v>
+      </c>
+      <c r="N109" s="6">
+        <v>177</v>
+      </c>
+      <c r="O109" s="6">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C110" s="3">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3">
+        <v>138</v>
+      </c>
+      <c r="K110" s="3">
+        <v>0</v>
+      </c>
+      <c r="L110" s="3">
+        <v>0</v>
+      </c>
+      <c r="M110" s="3">
+        <v>0</v>
+      </c>
+      <c r="N110" s="3">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C111" s="6">
+        <v>0</v>
+      </c>
+      <c r="D111" s="6">
+        <v>0</v>
+      </c>
+      <c r="E111" s="6">
+        <v>0</v>
+      </c>
+      <c r="F111" s="6">
+        <v>0</v>
+      </c>
+      <c r="G111" s="6">
+        <v>0</v>
+      </c>
+      <c r="H111" s="6">
+        <v>0</v>
+      </c>
+      <c r="I111" s="6">
+        <v>0</v>
+      </c>
+      <c r="J111" s="6">
+        <v>0</v>
+      </c>
+      <c r="K111" s="6">
+        <v>94</v>
+      </c>
+      <c r="L111" s="6">
+        <v>0</v>
+      </c>
+      <c r="M111" s="6">
+        <v>0</v>
+      </c>
+      <c r="N111" s="6">
+        <v>0</v>
+      </c>
+      <c r="O111" s="6">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C112" s="3">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3">
+        <v>0</v>
+      </c>
+      <c r="K112" s="3">
+        <v>94</v>
+      </c>
+      <c r="L112" s="3">
+        <v>0</v>
+      </c>
+      <c r="M112" s="3">
+        <v>0</v>
+      </c>
+      <c r="N112" s="3">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="6">
+        <v>0</v>
+      </c>
+      <c r="D113" s="6">
+        <v>0</v>
+      </c>
+      <c r="E113" s="6">
+        <v>0</v>
+      </c>
+      <c r="F113" s="6">
+        <v>0</v>
+      </c>
+      <c r="G113" s="6">
+        <v>0</v>
+      </c>
+      <c r="H113" s="6">
+        <v>0</v>
+      </c>
+      <c r="I113" s="6">
+        <v>0</v>
+      </c>
+      <c r="J113" s="6">
+        <v>0</v>
+      </c>
+      <c r="K113" s="6">
+        <v>94</v>
+      </c>
+      <c r="L113" s="6">
+        <v>0</v>
+      </c>
+      <c r="M113" s="6">
+        <v>0</v>
+      </c>
+      <c r="N113" s="6">
+        <v>0</v>
+      </c>
+      <c r="O113" s="6">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C114" s="3">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3">
+        <v>69</v>
+      </c>
+      <c r="K114" s="3">
+        <v>0</v>
+      </c>
+      <c r="L114" s="3">
+        <v>0</v>
+      </c>
+      <c r="M114" s="3">
+        <v>0</v>
+      </c>
+      <c r="N114" s="3">
+        <v>0</v>
+      </c>
+      <c r="O114" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" s="6">
+        <v>0</v>
+      </c>
+      <c r="D115" s="6">
+        <v>0</v>
+      </c>
+      <c r="E115" s="6">
+        <v>0</v>
+      </c>
+      <c r="F115" s="6">
+        <v>0</v>
+      </c>
+      <c r="G115" s="6">
+        <v>0</v>
+      </c>
+      <c r="H115" s="6">
+        <v>0</v>
+      </c>
+      <c r="I115" s="6">
+        <v>0</v>
+      </c>
+      <c r="J115" s="6">
+        <v>0</v>
+      </c>
+      <c r="K115" s="6">
+        <v>0</v>
+      </c>
+      <c r="L115" s="6">
+        <v>0</v>
+      </c>
+      <c r="M115" s="6">
+        <v>56</v>
+      </c>
+      <c r="N115" s="6">
+        <v>0</v>
+      </c>
+      <c r="O115" s="6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C116" s="3">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3">
+        <v>5</v>
+      </c>
+      <c r="L116" s="3">
+        <v>7</v>
+      </c>
+      <c r="M116" s="3">
+        <v>0</v>
+      </c>
+      <c r="N116" s="3">
+        <v>0</v>
+      </c>
+      <c r="O116" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C117" s="6">
+        <v>0</v>
+      </c>
+      <c r="D117" s="6">
+        <v>0</v>
+      </c>
+      <c r="E117" s="6">
+        <v>0</v>
+      </c>
+      <c r="F117" s="6">
+        <v>0</v>
+      </c>
+      <c r="G117" s="6">
+        <v>0</v>
+      </c>
+      <c r="H117" s="6">
+        <v>0</v>
+      </c>
+      <c r="I117" s="6">
+        <v>0</v>
+      </c>
+      <c r="J117" s="6">
+        <v>0</v>
+      </c>
+      <c r="K117" s="6">
+        <v>7</v>
+      </c>
+      <c r="L117" s="6">
+        <v>4</v>
+      </c>
+      <c r="M117" s="6">
+        <v>0</v>
+      </c>
+      <c r="N117" s="6">
+        <v>0</v>
+      </c>
+      <c r="O117" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C118" s="3">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3">
+        <v>0</v>
+      </c>
+      <c r="K118" s="3">
+        <v>9</v>
+      </c>
+      <c r="L118" s="3">
+        <v>0</v>
+      </c>
+      <c r="M118" s="3">
+        <v>0</v>
+      </c>
+      <c r="N118" s="3">
+        <v>0</v>
+      </c>
+      <c r="O118" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C119" s="6">
+        <v>0</v>
+      </c>
+      <c r="D119" s="6">
+        <v>0</v>
+      </c>
+      <c r="E119" s="6">
+        <v>0</v>
+      </c>
+      <c r="F119" s="6">
+        <v>0</v>
+      </c>
+      <c r="G119" s="6">
+        <v>0</v>
+      </c>
+      <c r="H119" s="6">
+        <v>0</v>
+      </c>
+      <c r="I119" s="6">
+        <v>0</v>
+      </c>
+      <c r="J119" s="6">
+        <v>0</v>
+      </c>
+      <c r="K119" s="6">
+        <v>3</v>
+      </c>
+      <c r="L119" s="6">
+        <v>0</v>
+      </c>
+      <c r="M119" s="6">
+        <v>0</v>
+      </c>
+      <c r="N119" s="6">
+        <v>0</v>
+      </c>
+      <c r="O119" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120" s="3">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3">
+        <v>0</v>
+      </c>
+      <c r="K120" s="3">
+        <v>0</v>
+      </c>
+      <c r="L120" s="3">
+        <v>0</v>
+      </c>
+      <c r="M120" s="3">
+        <v>0</v>
+      </c>
+      <c r="N120" s="3">
+        <v>2</v>
+      </c>
+      <c r="O120" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="24" customHeight="1">
+      <c r="A121" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B121" s="8"/>
+      <c r="C121" s="9">
+        <v>166288629</v>
+      </c>
+      <c r="D121" s="9">
+        <v>185012152</v>
+      </c>
+      <c r="E121" s="9">
+        <v>191335121</v>
+      </c>
+      <c r="F121" s="9">
+        <v>188233942</v>
+      </c>
+      <c r="G121" s="9">
+        <v>195168862</v>
+      </c>
+      <c r="H121" s="9">
+        <v>198037211</v>
+      </c>
+      <c r="I121" s="9">
+        <v>201332673</v>
+      </c>
+      <c r="J121" s="9">
+        <v>203518281</v>
+      </c>
+      <c r="K121" s="9">
+        <v>212277994</v>
+      </c>
+      <c r="L121" s="9">
+        <v>214305739</v>
+      </c>
+      <c r="M121" s="9">
+        <v>241392186</v>
+      </c>
+      <c r="N121" s="9">
+        <v>257876354</v>
+      </c>
+      <c r="O121" s="9">
+        <v>2454779145</v>
       </c>
     </row>
   </sheetData>
